--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,6 +1043,835 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125182464</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svarttjärnåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595770</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6925758</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125184693</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svarttjärnåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595784</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6925857</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125182172</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svarttjärnåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595788</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6925752</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125181960</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96979</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svarttjärnåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595845</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6925718</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125183914</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svarttjärnåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595860</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6925746</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125182579</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svarttjärnåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595762</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6925767</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125183075</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svarttjärnåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>595759</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6925818</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125182464</v>
+        <v>125181960</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,43 +1058,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595770</v>
+        <v>595845</v>
       </c>
       <c r="R5" t="n">
-        <v>6925758</v>
+        <v>6925718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1158,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125184693</v>
+        <v>125183914</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1199,7 +1194,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595784</v>
+        <v>595860</v>
       </c>
       <c r="R6" t="n">
-        <v>6925857</v>
+        <v>6925746</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1285,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125182172</v>
+        <v>125183075</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,34 +1296,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595788</v>
+        <v>595759</v>
       </c>
       <c r="R7" t="n">
-        <v>6925752</v>
+        <v>6925818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1370,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125181960</v>
+        <v>125184693</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,38 +1414,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595845</v>
+        <v>595784</v>
       </c>
       <c r="R8" t="n">
-        <v>6925718</v>
+        <v>6925857</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1492,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125183914</v>
+        <v>125182172</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,39 +1540,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595860</v>
+        <v>595788</v>
       </c>
       <c r="R9" t="n">
-        <v>6925746</v>
+        <v>6925752</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,12 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125182579</v>
+        <v>125182464</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,16 +1652,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1667,7 +1672,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1676,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595762</v>
+        <v>595770</v>
       </c>
       <c r="R10" t="n">
-        <v>6925767</v>
+        <v>6925758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1721,12 +1726,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:33</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,7 +1753,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125183075</v>
+        <v>125182579</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595759</v>
+        <v>595762</v>
       </c>
       <c r="R11" t="n">
-        <v>6925818</v>
+        <v>6925767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125181960</v>
+        <v>125184693</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,38 +1058,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595845</v>
+        <v>595784</v>
       </c>
       <c r="R5" t="n">
-        <v>6925718</v>
+        <v>6925857</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1136,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1280,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125183075</v>
+        <v>125182464</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,16 +1306,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1316,7 +1326,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1325,10 +1335,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595759</v>
+        <v>595770</v>
       </c>
       <c r="R7" t="n">
-        <v>6925818</v>
+        <v>6925758</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1370,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,12 +1380,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125184693</v>
+        <v>125181960</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,43 +1419,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595784</v>
+        <v>595845</v>
       </c>
       <c r="R8" t="n">
-        <v>6925857</v>
+        <v>6925718</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,12 +1492,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1636,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125182464</v>
+        <v>125183075</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,16 +1647,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1672,7 +1667,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595770</v>
+        <v>595759</v>
       </c>
       <c r="R10" t="n">
-        <v>6925758</v>
+        <v>6925818</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1711,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,7 +1721,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125184693</v>
+        <v>125182172</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,39 +1062,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595784</v>
+        <v>595788</v>
       </c>
       <c r="R5" t="n">
-        <v>6925857</v>
+        <v>6925752</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125183914</v>
+        <v>125182464</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,16 +1174,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1213,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595860</v>
+        <v>595770</v>
       </c>
       <c r="R6" t="n">
-        <v>6925746</v>
+        <v>6925758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,12 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125182464</v>
+        <v>125182579</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,16 +1291,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1326,7 +1311,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1335,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595770</v>
+        <v>595762</v>
       </c>
       <c r="R7" t="n">
-        <v>6925758</v>
+        <v>6925767</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,7 +1365,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125181960</v>
+        <v>125184693</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,38 +1409,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595845</v>
+        <v>595784</v>
       </c>
       <c r="R8" t="n">
-        <v>6925718</v>
+        <v>6925857</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,7 +1487,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125182172</v>
+        <v>125183075</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,34 +1535,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595788</v>
+        <v>595759</v>
       </c>
       <c r="R9" t="n">
-        <v>6925752</v>
+        <v>6925818</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1609,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,10 +1641,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125183075</v>
+        <v>125181960</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1643,43 +1653,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595759</v>
+        <v>595845</v>
       </c>
       <c r="R10" t="n">
-        <v>6925818</v>
+        <v>6925718</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1721,12 +1726,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,7 +1753,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125182579</v>
+        <v>125183914</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1789,7 +1789,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595762</v>
+        <v>595860</v>
       </c>
       <c r="R11" t="n">
-        <v>6925767</v>
+        <v>6925746</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125182172</v>
+        <v>125184693</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,34 +1062,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595788</v>
+        <v>595784</v>
       </c>
       <c r="R5" t="n">
-        <v>6925752</v>
+        <v>6925857</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1136,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125182464</v>
+        <v>125182172</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,39 +1184,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595770</v>
+        <v>595788</v>
       </c>
       <c r="R6" t="n">
-        <v>6925758</v>
+        <v>6925752</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125182579</v>
+        <v>125183914</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1311,7 +1316,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595762</v>
+        <v>595860</v>
       </c>
       <c r="R7" t="n">
-        <v>6925767</v>
+        <v>6925746</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1397,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125184693</v>
+        <v>125182464</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,16 +1418,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1433,7 +1438,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1442,10 +1447,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595784</v>
+        <v>595770</v>
       </c>
       <c r="R8" t="n">
-        <v>6925857</v>
+        <v>6925758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,12 +1492,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125183075</v>
+        <v>125181960</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,43 +1531,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595759</v>
+        <v>595845</v>
       </c>
       <c r="R9" t="n">
-        <v>6925818</v>
+        <v>6925718</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,12 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1641,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125181960</v>
+        <v>125183075</v>
       </c>
       <c r="B10" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,38 +1643,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595845</v>
+        <v>595759</v>
       </c>
       <c r="R10" t="n">
-        <v>6925718</v>
+        <v>6925818</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1711,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,7 +1721,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,7 +1753,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125183914</v>
+        <v>125182579</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1789,7 +1789,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595860</v>
+        <v>595762</v>
       </c>
       <c r="R11" t="n">
-        <v>6925746</v>
+        <v>6925767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125184693</v>
+        <v>125183914</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1082,7 +1082,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595784</v>
+        <v>595860</v>
       </c>
       <c r="R5" t="n">
-        <v>6925857</v>
+        <v>6925746</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1168,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125182172</v>
+        <v>125184693</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,34 +1184,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595788</v>
+        <v>595784</v>
       </c>
       <c r="R6" t="n">
-        <v>6925752</v>
+        <v>6925857</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1258,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125183914</v>
+        <v>125182172</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,39 +1306,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595860</v>
+        <v>595788</v>
       </c>
       <c r="R7" t="n">
-        <v>6925746</v>
+        <v>6925752</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,12 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125182464</v>
+        <v>125181960</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,43 +1414,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595770</v>
+        <v>595845</v>
       </c>
       <c r="R8" t="n">
-        <v>6925758</v>
+        <v>6925718</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125181960</v>
+        <v>125182579</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,38 +1526,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595845</v>
+        <v>595762</v>
       </c>
       <c r="R9" t="n">
-        <v>6925718</v>
+        <v>6925767</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1604,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125183075</v>
+        <v>125182464</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,16 +1652,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1667,7 +1672,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1676,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595759</v>
+        <v>595770</v>
       </c>
       <c r="R10" t="n">
-        <v>6925818</v>
+        <v>6925758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1721,12 +1726,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,7 +1753,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125182579</v>
+        <v>125183075</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595762</v>
+        <v>595759</v>
       </c>
       <c r="R11" t="n">
-        <v>6925767</v>
+        <v>6925818</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>125183914</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1168,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125184693</v>
+        <v>125182172</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,39 +1184,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595784</v>
+        <v>595788</v>
       </c>
       <c r="R6" t="n">
-        <v>6925857</v>
+        <v>6925752</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,12 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125182172</v>
+        <v>125181960</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>97147</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,25 +1292,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1330,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595788</v>
+        <v>595845</v>
       </c>
       <c r="R7" t="n">
-        <v>6925752</v>
+        <v>6925718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125181960</v>
+        <v>125182579</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,38 +1404,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595845</v>
+        <v>595762</v>
       </c>
       <c r="R8" t="n">
-        <v>6925718</v>
+        <v>6925767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1482,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125182579</v>
+        <v>125182464</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57632</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,16 +1530,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595762</v>
+        <v>595770</v>
       </c>
       <c r="R9" t="n">
-        <v>6925767</v>
+        <v>6925758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,12 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:33</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125182464</v>
+        <v>125184693</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,16 +1647,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1672,7 +1667,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1681,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595770</v>
+        <v>595784</v>
       </c>
       <c r="R10" t="n">
-        <v>6925758</v>
+        <v>6925857</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1711,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,7 +1721,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,7 +1756,7 @@
         <v>125183075</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125182579</v>
+        <v>125182464</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595762</v>
+        <v>595770</v>
       </c>
       <c r="R8" t="n">
-        <v>6925767</v>
+        <v>6925758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,12 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:33</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125182464</v>
+        <v>125182579</v>
       </c>
       <c r="B9" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,16 +1525,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1550,7 +1545,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1559,10 +1554,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595770</v>
+        <v>595762</v>
       </c>
       <c r="R9" t="n">
-        <v>6925758</v>
+        <v>6925767</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1599,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125183914</v>
+        <v>125182579</v>
       </c>
       <c r="B5" t="n">
         <v>57635</v>
@@ -1082,7 +1082,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595860</v>
+        <v>595762</v>
       </c>
       <c r="R5" t="n">
-        <v>6925746</v>
+        <v>6925767</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1168,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125182172</v>
+        <v>125183075</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,34 +1184,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595788</v>
+        <v>595759</v>
       </c>
       <c r="R6" t="n">
-        <v>6925752</v>
+        <v>6925818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1258,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1392,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125182464</v>
+        <v>125183914</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,16 +1418,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1437,10 +1447,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595770</v>
+        <v>595860</v>
       </c>
       <c r="R8" t="n">
-        <v>6925758</v>
+        <v>6925746</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1492,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,7 +1524,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125182579</v>
+        <v>125184693</v>
       </c>
       <c r="B9" t="n">
         <v>57635</v>
@@ -1554,10 +1569,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595762</v>
+        <v>595784</v>
       </c>
       <c r="R9" t="n">
-        <v>6925767</v>
+        <v>6925857</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,7 +1614,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1631,10 +1646,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125184693</v>
+        <v>125182172</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,39 +1662,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595784</v>
+        <v>595788</v>
       </c>
       <c r="R10" t="n">
-        <v>6925857</v>
+        <v>6925752</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,7 +1721,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1721,12 +1731,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125183075</v>
+        <v>125182464</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1769,16 +1774,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1789,7 +1794,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1798,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595759</v>
+        <v>595770</v>
       </c>
       <c r="R11" t="n">
-        <v>6925818</v>
+        <v>6925758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,7 +1838,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1843,12 +1848,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1046,55 +1046,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125182579</v>
+        <v>125181960</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595762</v>
+        <v>595845</v>
       </c>
       <c r="R5" t="n">
-        <v>6925767</v>
+        <v>6925718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:33</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,15 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125183075</v>
+        <v>125182172</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,39 +1164,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595759</v>
+        <v>595788</v>
       </c>
       <c r="R6" t="n">
-        <v>6925818</v>
+        <v>6925752</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,50 +1260,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125181960</v>
+        <v>125184693</v>
       </c>
       <c r="B7" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595845</v>
+        <v>595784</v>
       </c>
       <c r="R7" t="n">
-        <v>6925718</v>
+        <v>6925857</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,15 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125183914</v>
+        <v>125183075</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1408,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1447,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595860</v>
+        <v>595759</v>
       </c>
       <c r="R8" t="n">
-        <v>6925746</v>
+        <v>6925818</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1524,15 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125184693</v>
+        <v>125182464</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,16 +1505,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1560,7 +1525,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1569,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595784</v>
+        <v>595770</v>
       </c>
       <c r="R9" t="n">
-        <v>6925857</v>
+        <v>6925758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1614,12 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,15 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125182172</v>
+        <v>125182579</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,34 +1617,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595788</v>
+        <v>595762</v>
       </c>
       <c r="R10" t="n">
-        <v>6925752</v>
+        <v>6925767</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1731,7 +1691,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,15 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125182464</v>
+        <v>125183914</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,16 +1734,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1803,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595770</v>
+        <v>595860</v>
       </c>
       <c r="R11" t="n">
-        <v>6925758</v>
+        <v>6925746</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1838,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1848,7 +1808,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>125181960</v>
       </c>
       <c r="B5" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125182172</v>
+        <v>125184693</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,34 +1164,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595788</v>
+        <v>595784</v>
       </c>
       <c r="R6" t="n">
-        <v>6925752</v>
+        <v>6925857</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1238,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125184693</v>
+        <v>125183075</v>
       </c>
       <c r="B7" t="n">
         <v>57651</v>
@@ -1300,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595784</v>
+        <v>595759</v>
       </c>
       <c r="R7" t="n">
-        <v>6925857</v>
+        <v>6925818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1377,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125183075</v>
+        <v>125182172</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,39 +1398,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595759</v>
+        <v>595788</v>
       </c>
       <c r="R8" t="n">
-        <v>6925818</v>
+        <v>6925752</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>125182464</v>
       </c>
       <c r="B9" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>125182464</v>
       </c>
       <c r="B9" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>125182464</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>125182464</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>125182464</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>125182464</v>
       </c>
       <c r="B9" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>125184693</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>125183075</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>125182579</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>125183914</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>125184693</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>125183075</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>125182579</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>125183914</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>104442680</v>
       </c>
       <c r="B2" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595804.4148185472</v>
+        <v>595805</v>
       </c>
       <c r="R2" t="n">
-        <v>6925791.870041097</v>
+        <v>6925792</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>104442682</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595767.3307646359</v>
+        <v>595767</v>
       </c>
       <c r="R3" t="n">
-        <v>6925888.058172535</v>
+        <v>6925888</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +854,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,65 +897,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120670079</v>
+        <v>125182172</v>
       </c>
       <c r="B4" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Talltita, Svarttjärnåsen, Sättna, Mpd</t>
+          <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595830</v>
+        <v>595788</v>
       </c>
       <c r="R4" t="n">
-        <v>6925817</v>
+        <v>6925752</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,17 +962,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flög runt och letade mat i träden.</t>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125181960</v>
+        <v>125182464</v>
       </c>
       <c r="B5" t="n">
-        <v>97209</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,34 +1015,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595845</v>
+        <v>595770</v>
       </c>
       <c r="R5" t="n">
-        <v>6925718</v>
+        <v>6925758</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125184693</v>
+        <v>125182579</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595784</v>
+        <v>595762</v>
       </c>
       <c r="R6" t="n">
-        <v>6925857</v>
+        <v>6925767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1273,7 +1236,7 @@
         <v>125183075</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125182172</v>
+        <v>125183914</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,34 +1361,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595788</v>
+        <v>595860</v>
       </c>
       <c r="R8" t="n">
-        <v>6925752</v>
+        <v>6925746</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1435,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125182464</v>
+        <v>125184693</v>
       </c>
       <c r="B9" t="n">
-        <v>57681</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,16 +1478,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1525,7 +1498,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595770</v>
+        <v>595784</v>
       </c>
       <c r="R9" t="n">
-        <v>6925758</v>
+        <v>6925857</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1552,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125182579</v>
+        <v>120670079</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,42 +1595,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnåsen, Mpd</t>
+          <t>Talltita, Svarttjärnåsen, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595762</v>
+        <v>595830</v>
       </c>
       <c r="R10" t="n">
-        <v>6925767</v>
+        <v>6925817</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,27 +1661,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:33</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:33</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Flög runt och letade mat i träden.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,50 +1698,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125183914</v>
+        <v>125181960</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>97983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svarttjärnåsen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595860</v>
+        <v>595845</v>
       </c>
       <c r="R11" t="n">
-        <v>6925746</v>
+        <v>6925718</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,12 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46087-2024 artfynd.xlsx
+++ b/artfynd/A 46087-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104442680</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104442682</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125182172</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125182464</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125182579</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125183075</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,6 +1499,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125183914</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125184693</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1695,6 +1740,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120670079</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1802,8 +1852,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125181960</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>